--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49234,6 +49234,14 @@
         <v>14190.0</v>
       </c>
     </row>
+    <row r="6154">
+      <c r="A6154" t="str">
+        <v>2026-09-06</v>
+      </c>
+      <c r="B6154">
+        <v>14190.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49242,6 +49242,14 @@
         <v>14190.0</v>
       </c>
     </row>
+    <row r="6155">
+      <c r="A6155" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="B6155">
+        <v>14190.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49247,7 +49247,15 @@
         <v>2026-09-07</v>
       </c>
       <c r="B6155">
-        <v>14190.0</v>
+        <v>14130.0</v>
+      </c>
+    </row>
+    <row r="6156">
+      <c r="A6156" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B6156">
+        <v>14240.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49258,6 +49258,14 @@
         <v>14240.0</v>
       </c>
     </row>
+    <row r="6157">
+      <c r="A6157" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="B6157">
+        <v>14145.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49266,6 +49266,14 @@
         <v>14145.0</v>
       </c>
     </row>
+    <row r="6158">
+      <c r="A6158" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B6158">
+        <v>14255.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49274,6 +49274,14 @@
         <v>14255.0</v>
       </c>
     </row>
+    <row r="6159">
+      <c r="A6159" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="B6159">
+        <v>14015.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49279,7 +49279,15 @@
         <v>2026-09-11</v>
       </c>
       <c r="B6159">
-        <v>14015.0</v>
+        <v>14155.0</v>
+      </c>
+    </row>
+    <row r="6160">
+      <c r="A6160" t="str">
+        <v>2026-09-12</v>
+      </c>
+      <c r="B6160">
+        <v>14155.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49290,6 +49290,22 @@
         <v>14155.0</v>
       </c>
     </row>
+    <row r="6161">
+      <c r="A6161" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="B6161">
+        <v>14155.0</v>
+      </c>
+    </row>
+    <row r="6162">
+      <c r="A6162" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B6162">
+        <v>14125.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49303,7 +49303,15 @@
         <v>2026-09-14</v>
       </c>
       <c r="B6162">
-        <v>14125.0</v>
+        <v>14010.0</v>
+      </c>
+    </row>
+    <row r="6163">
+      <c r="A6163" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="B6163">
+        <v>14040.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49314,6 +49314,14 @@
         <v>14040.0</v>
       </c>
     </row>
+    <row r="6164">
+      <c r="A6164" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="B6164">
+        <v>14065.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49322,6 +49322,14 @@
         <v>14065.0</v>
       </c>
     </row>
+    <row r="6165">
+      <c r="A6165" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B6165">
+        <v>14010.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49330,6 +49330,14 @@
         <v>14010.0</v>
       </c>
     </row>
+    <row r="6166">
+      <c r="A6166" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B6166">
+        <v>14155.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49338,6 +49338,14 @@
         <v>14155.0</v>
       </c>
     </row>
+    <row r="6167">
+      <c r="A6167" t="str">
+        <v>2026-09-19</v>
+      </c>
+      <c r="B6167">
+        <v>14285.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49346,6 +49346,14 @@
         <v>14285.0</v>
       </c>
     </row>
+    <row r="6168">
+      <c r="A6168" t="str">
+        <v>2026-09-20</v>
+      </c>
+      <c r="B6168">
+        <v>14285.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49354,6 +49354,14 @@
         <v>14285.0</v>
       </c>
     </row>
+    <row r="6169">
+      <c r="A6169" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="B6169">
+        <v>14270.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49359,7 +49359,15 @@
         <v>2026-09-21</v>
       </c>
       <c r="B6169">
-        <v>14270.0</v>
+        <v>14170.0</v>
+      </c>
+    </row>
+    <row r="6170">
+      <c r="A6170" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="B6170">
+        <v>14185.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49367,7 +49367,23 @@
         <v>2026-09-22</v>
       </c>
       <c r="B6170">
-        <v>14185.0</v>
+        <v>14055.0</v>
+      </c>
+    </row>
+    <row r="6171">
+      <c r="A6171" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="B6171">
+        <v>14135.0</v>
+      </c>
+    </row>
+    <row r="6172">
+      <c r="A6172" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="B6172">
+        <v>13995.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49386,6 +49386,14 @@
         <v>13995.0</v>
       </c>
     </row>
+    <row r="6173">
+      <c r="A6173" t="str">
+        <v>2026-09-25</v>
+      </c>
+      <c r="B6173">
+        <v>14010.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49394,6 +49394,14 @@
         <v>14010.0</v>
       </c>
     </row>
+    <row r="6174">
+      <c r="A6174" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="B6174">
+        <v>13995.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49402,6 +49402,14 @@
         <v>13995.0</v>
       </c>
     </row>
+    <row r="6175">
+      <c r="A6175" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B6175">
+        <v>13995.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49410,6 +49410,14 @@
         <v>13995.0</v>
       </c>
     </row>
+    <row r="6176">
+      <c r="A6176" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="B6176">
+        <v>13765.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49415,7 +49415,15 @@
         <v>2026-09-28</v>
       </c>
       <c r="B6176">
-        <v>13765.0</v>
+        <v>13665.0</v>
+      </c>
+    </row>
+    <row r="6177">
+      <c r="A6177" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B6177">
+        <v>13640.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49426,6 +49426,14 @@
         <v>13640.0</v>
       </c>
     </row>
+    <row r="6178">
+      <c r="A6178" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B6178">
+        <v>13710.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49434,6 +49434,14 @@
         <v>13710.0</v>
       </c>
     </row>
+    <row r="6179">
+      <c r="A6179" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B6179">
+        <v>13680.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49442,6 +49442,14 @@
         <v>13680.0</v>
       </c>
     </row>
+    <row r="6180">
+      <c r="A6180" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="B6180">
+        <v>13775.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49450,6 +49450,14 @@
         <v>13775.0</v>
       </c>
     </row>
+    <row r="6181">
+      <c r="A6181" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="B6181">
+        <v>13675.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49458,6 +49458,14 @@
         <v>13675.0</v>
       </c>
     </row>
+    <row r="6182">
+      <c r="A6182" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B6182">
+        <v>13675.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49466,6 +49466,22 @@
         <v>13675.0</v>
       </c>
     </row>
+    <row r="6183">
+      <c r="A6183" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B6183">
+        <v>13675.0</v>
+      </c>
+    </row>
+    <row r="6184">
+      <c r="A6184" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="B6184">
+        <v>13660.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49479,7 +49479,15 @@
         <v>2026-10-06</v>
       </c>
       <c r="B6184">
-        <v>13660.0</v>
+        <v>13770.0</v>
+      </c>
+    </row>
+    <row r="6185">
+      <c r="A6185" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B6185">
+        <v>13710.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49490,6 +49490,14 @@
         <v>13710.0</v>
       </c>
     </row>
+    <row r="6186">
+      <c r="A6186" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="B6186">
+        <v>13710.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49498,6 +49498,14 @@
         <v>13710.0</v>
       </c>
     </row>
+    <row r="6187">
+      <c r="A6187" t="str">
+        <v>2026-10-09</v>
+      </c>
+      <c r="B6187">
+        <v>13815.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49506,6 +49506,14 @@
         <v>13815.0</v>
       </c>
     </row>
+    <row r="6188">
+      <c r="A6188" t="str">
+        <v>2026-10-10</v>
+      </c>
+      <c r="B6188">
+        <v>13880.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49514,6 +49514,14 @@
         <v>13880.0</v>
       </c>
     </row>
+    <row r="6189">
+      <c r="A6189" t="str">
+        <v>2026-10-11</v>
+      </c>
+      <c r="B6189">
+        <v>13880.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49522,6 +49522,14 @@
         <v>13880.0</v>
       </c>
     </row>
+    <row r="6190">
+      <c r="A6190" t="str">
+        <v>2026-10-12</v>
+      </c>
+      <c r="B6190">
+        <v>13840.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49527,7 +49527,15 @@
         <v>2026-10-12</v>
       </c>
       <c r="B6190">
-        <v>13840.0</v>
+        <v>13720.0</v>
+      </c>
+    </row>
+    <row r="6191">
+      <c r="A6191" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="B6191">
+        <v>13685.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49538,6 +49538,14 @@
         <v>13685.0</v>
       </c>
     </row>
+    <row r="6192">
+      <c r="A6192" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="B6192">
+        <v>13590.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49546,6 +49546,14 @@
         <v>13590.0</v>
       </c>
     </row>
+    <row r="6193">
+      <c r="A6193" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="B6193">
+        <v>13515.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49554,6 +49554,14 @@
         <v>13515.0</v>
       </c>
     </row>
+    <row r="6194">
+      <c r="A6194" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="B6194">
+        <v>13515.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49562,6 +49562,14 @@
         <v>13515.0</v>
       </c>
     </row>
+    <row r="6195">
+      <c r="A6195" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="B6195">
+        <v>13535.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49570,6 +49570,14 @@
         <v>13535.0</v>
       </c>
     </row>
+    <row r="6196">
+      <c r="A6196" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="B6196">
+        <v>13535.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49578,6 +49578,14 @@
         <v>13535.0</v>
       </c>
     </row>
+    <row r="6197">
+      <c r="A6197" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="B6197">
+        <v>13570.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49586,6 +49586,14 @@
         <v>13570.0</v>
       </c>
     </row>
+    <row r="6198">
+      <c r="A6198" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="B6198">
+        <v>13490.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49591,7 +49591,15 @@
         <v>2026-10-20</v>
       </c>
       <c r="B6198">
-        <v>13490.0</v>
+        <v>13390.0</v>
+      </c>
+    </row>
+    <row r="6199">
+      <c r="A6199" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="B6199">
+        <v>13390.0</v>
       </c>
     </row>
   </sheetData>

--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49602,6 +49602,14 @@
         <v>13390.0</v>
       </c>
     </row>
+    <row r="6200">
+      <c r="A6200" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="B6200">
+        <v>13235.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49610,6 +49610,14 @@
         <v>13235.0</v>
       </c>
     </row>
+    <row r="6201">
+      <c r="A6201" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="B6201">
+        <v>13060.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49618,6 +49618,14 @@
         <v>13060.0</v>
       </c>
     </row>
+    <row r="6202">
+      <c r="A6202" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="B6202">
+        <v>13070.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49626,6 +49626,14 @@
         <v>13070.0</v>
       </c>
     </row>
+    <row r="6203">
+      <c r="A6203" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="B6203">
+        <v>13070.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49634,6 +49634,14 @@
         <v>13070.0</v>
       </c>
     </row>
+    <row r="6204">
+      <c r="A6204" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="B6204">
+        <v>13085.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49642,6 +49642,14 @@
         <v>13085.0</v>
       </c>
     </row>
+    <row r="6205">
+      <c r="A6205" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="B6205">
+        <v>13135.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49650,6 +49650,14 @@
         <v>13135.0</v>
       </c>
     </row>
+    <row r="6206">
+      <c r="A6206" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="B6206">
+        <v>13195.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49658,6 +49658,14 @@
         <v>13195.0</v>
       </c>
     </row>
+    <row r="6207">
+      <c r="A6207" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="B6207">
+        <v>13195.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/gold_rates.xlsx
+++ b/gold_rates.xlsx
@@ -49666,6 +49666,14 @@
         <v>13195.0</v>
       </c>
     </row>
+    <row r="6208">
+      <c r="A6208" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="B6208">
+        <v>13040.0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>